--- a/analise_eua/energia_eletrica/constellation/ceg_10q.xlsx
+++ b/analise_eua/energia_eletrica/constellation/ceg_10q.xlsx
@@ -433,47 +433,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -484,42 +487,45 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>697</v>
+      </c>
+      <c r="C2" t="n">
         <v>800</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>3959</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1974</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1846</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1793</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>311</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>562</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1889</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>269</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>237</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1192</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>806</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1605</v>
       </c>
     </row>
@@ -530,42 +536,45 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>380</v>
+      </c>
+      <c r="C3" t="n">
         <v>371</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>132</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>88</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>96</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>89</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>72</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>83</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>88</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>56</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>99</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>111</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>120</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>91</v>
       </c>
     </row>
@@ -576,42 +585,45 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4661</v>
+      </c>
+      <c r="C4" t="n">
         <v>4414</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>3168</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2947</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3193</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1208</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1578</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1855</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1541</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1306</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2147</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1819</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1734</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1936</v>
       </c>
     </row>
@@ -622,42 +634,45 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2167</v>
+      </c>
+      <c r="C5" t="n">
         <v>1795</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>632</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>726</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>858</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>632</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>935</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1232</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1467</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>1733</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1952</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2557</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1990</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>1775</v>
       </c>
     </row>
@@ -668,11 +683,11 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3368</v>
+      </c>
+      <c r="C6" t="n">
         <v>2582</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
@@ -704,6 +719,9 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -714,42 +732,45 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>784</v>
+      </c>
+      <c r="C7" t="n">
         <v>1038</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>786</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>628</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>914</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>700</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>487</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>805</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>593</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>436</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>720</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>524</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>355</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>577</v>
       </c>
     </row>
@@ -760,11 +781,11 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5743</v>
+      </c>
+      <c r="C8" t="n">
         <v>5735</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
@@ -796,6 +817,9 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -806,42 +830,45 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1165</v>
+      </c>
+      <c r="C9" t="n">
         <v>1274</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>696</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>714</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>778</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>2819</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2394</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>2066</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>2179</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>1742</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>1067</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1607</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1317</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>1238</v>
       </c>
     </row>
@@ -852,42 +879,45 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>18965</v>
+      </c>
+      <c r="C10" t="n">
         <v>18009</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>11649</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>9233</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>9631</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>9270</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>7852</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>8460</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9902</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>7575</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>8108</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>9853</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>8090</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>8767</v>
       </c>
     </row>
@@ -898,42 +928,45 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>41228</v>
+      </c>
+      <c r="C11" t="n">
         <v>40769</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>21990</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>21820</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>21566</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>20892</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>21973</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>22446</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>20849</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>20239</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>20074</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>19705</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>19739</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>19837</v>
       </c>
     </row>
@@ -944,42 +977,45 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>20492</v>
+      </c>
+      <c r="C12" t="n">
         <v>19366</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>18985</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>18289</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>17472</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>17694</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>16883</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>16916</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>14573</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>14821</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>14606</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>13453</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>14001</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>15272</v>
       </c>
     </row>
@@ -993,7 +1029,7 @@
         <v>11527</v>
       </c>
       <c r="C13" t="n">
-        <v>420</v>
+        <v>11527</v>
       </c>
       <c r="D13" t="n">
         <v>420</v>
@@ -1008,11 +1044,11 @@
         <v>420</v>
       </c>
       <c r="H13" t="n">
+        <v>420</v>
+      </c>
+      <c r="I13" t="n">
         <v>425</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
@@ -1026,6 +1062,9 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1036,42 +1075,45 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>1741</v>
+      </c>
+      <c r="C14" t="n">
         <v>2113</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>459</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>527</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>485</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>732</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>993</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>774</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>970</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1067</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1125</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1252</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1121</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>565</v>
       </c>
     </row>
@@ -1082,42 +1124,45 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>4300</v>
+      </c>
+      <c r="C15" t="n">
         <v>5127</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>2231</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>2351</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>2292</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>2297</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>2610</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>2332</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>1901</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>2167</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>1977</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2137</v>
       </c>
       <c r="M15" t="n">
         <v>2137</v>
       </c>
       <c r="N15" t="n">
+        <v>2137</v>
+      </c>
+      <c r="O15" t="n">
         <v>2152</v>
       </c>
     </row>
@@ -1128,42 +1173,45 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>38060</v>
+      </c>
+      <c r="C16" t="n">
         <v>38133</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>22522</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>21985</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>21055</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>21672</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>21515</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>21108</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>18214</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>18745</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17976</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>17058</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>17504</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>18242</v>
       </c>
     </row>
@@ -1174,42 +1222,45 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>98253</v>
+      </c>
+      <c r="C17" t="n">
         <v>96911</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>56161</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>53038</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>52252</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>51834</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>51340</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>52014</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>48965</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>46559</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>46158</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>46616</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>45333</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>46846</v>
       </c>
     </row>
@@ -1220,42 +1271,45 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5226</v>
+      </c>
+      <c r="C18" t="n">
         <v>5102</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1650</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>900</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>680</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1509</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>527</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>935</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>705</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>693</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>200</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>1080</v>
       </c>
     </row>
@@ -1266,42 +1320,45 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>363</v>
+      </c>
+      <c r="C19" t="n">
         <v>370</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>118</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>125</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1037</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>1034</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1035</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>122</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>116</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>110</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>161</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>181</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>184</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>191</v>
       </c>
     </row>
@@ -1312,42 +1369,45 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>4432</v>
+      </c>
+      <c r="C20" t="n">
         <v>4449</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>3926</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>3659</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>3614</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>2685</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>2422</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>2417</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>2252</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>744</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>743</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>933</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>749</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>803</v>
       </c>
     </row>
@@ -1358,42 +1418,45 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>716</v>
+      </c>
+      <c r="C21" t="n">
         <v>810</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>474</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>407</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>550</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>502</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>563</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>667</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>1108</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>1179</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1573</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2392</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1673</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>1469</v>
       </c>
     </row>
@@ -1404,42 +1467,45 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>927</v>
+      </c>
+      <c r="C22" t="n">
         <v>1193</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>956</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>806</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1001</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>909</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>730</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>895</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>857</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>673</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>865</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>773</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>587</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>727</v>
       </c>
     </row>
@@ -1450,42 +1516,45 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>1368</v>
+      </c>
+      <c r="C23" t="n">
         <v>1291</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>331</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>359</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>343</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>322</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>371</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>312</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>403</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>324</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>342</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>318</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>325</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>317</v>
       </c>
     </row>
@@ -1496,42 +1565,45 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>13032</v>
+      </c>
+      <c r="C24" t="n">
         <v>13215</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>7455</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>6256</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>6545</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>5452</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>5801</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5922</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>5263</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>5225</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5947</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>7887</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>5878</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>6434</v>
       </c>
     </row>
@@ -1542,42 +1614,45 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>19111</v>
+      </c>
+      <c r="C25" t="n">
         <v>16994</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>7269</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>7286</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>7321</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>7378</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>7409</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>8352</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>7512</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>6156</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5763</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>4480</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>4507</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>4548</v>
       </c>
     </row>
@@ -1588,42 +1663,45 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>8513</v>
+      </c>
+      <c r="C26" t="n">
         <v>8199</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>3578</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>3348</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>3226</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>3554</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>3377</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3208</v>
       </c>
       <c r="I26" t="n">
         <v>3208</v>
       </c>
       <c r="J26" t="n">
+        <v>3208</v>
+      </c>
+      <c r="K26" t="n">
         <v>3203</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>2982</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2647</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>2855</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>3247</v>
       </c>
     </row>
@@ -1634,42 +1712,45 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>12612</v>
+      </c>
+      <c r="C27" t="n">
         <v>12433</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>13032</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>12679</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>12524</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>12322</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>13510</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>14278</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>13797</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>12971</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>12831</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>12564</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>13402</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>13276</v>
       </c>
     </row>
@@ -1680,44 +1761,47 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>1844</v>
+      </c>
+      <c r="C28" t="n">
         <v>1835</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>1767</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>1763</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>1755</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>774</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>749</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>746</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>642</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>638</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>633</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>861</v>
-      </c>
-      <c r="M28" t="n">
-        <v>862</v>
       </c>
       <c r="N28" t="n">
         <v>862</v>
       </c>
+      <c r="O28" t="n">
+        <v>862</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1726,42 +1810,45 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>5914</v>
+      </c>
+      <c r="C29" t="n">
         <v>5389</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>5222</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>4939</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>4593</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>4828</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4310</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>3874</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>2923</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>3120</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>3069</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2658</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>2265</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>2969</v>
       </c>
     </row>
@@ -1772,42 +1859,45 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>601</v>
+      </c>
+      <c r="C30" t="n">
         <v>518</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>440</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>419</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>358</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>341</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>555</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>480</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>536</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>613</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>700</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>1244</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>1070</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>773</v>
       </c>
     </row>
@@ -1818,42 +1908,45 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>4304</v>
+      </c>
+      <c r="C31" t="n">
         <v>4508</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>1294</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>1148</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>1215</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>2028</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>1640</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>1393</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1196</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>1123</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1258</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>1251</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1210</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>1300</v>
       </c>
     </row>
@@ -1864,42 +1957,45 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>33788</v>
+      </c>
+      <c r="C32" t="n">
         <v>32882</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>26745</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>25693</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>25052</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>26063</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>26349</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>26180</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>24190</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>23566</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>23362</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>23080</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>23559</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>24359</v>
       </c>
     </row>
@@ -1910,42 +2006,45 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>65931</v>
+      </c>
+      <c r="C33" t="n">
         <v>63091</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>41469</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>39235</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>38918</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>38893</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>39559</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>40454</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>36965</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>34947</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>35072</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>35447</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>33944</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>35341</v>
       </c>
     </row>
@@ -1956,42 +2055,45 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>7692</v>
+      </c>
+      <c r="C34" t="n">
         <v>7334</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>5588</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>4779</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>4062</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>3325</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>2236</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>1532</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>887</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>248</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>-493</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>-483</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>-249</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>-91</v>
       </c>
     </row>
@@ -2002,42 +2104,45 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>-2398</v>
+      </c>
+      <c r="C35" t="n">
         <v>-2425</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>-2260</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>-2272</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>-2309</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>-2134</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>-2161</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>-2180</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>-1797</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>-1800</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>-1808</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>-1969</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>-1992</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>-2016</v>
       </c>
     </row>
@@ -2048,42 +2153,45 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>25737</v>
+      </c>
+      <c r="C36" t="n">
         <v>27677</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>10144</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>10091</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>10388</v>
-      </c>
-      <c r="F36" t="n">
-        <v>10538</v>
       </c>
       <c r="G36" t="n">
         <v>10538</v>
       </c>
       <c r="H36" t="n">
+        <v>10538</v>
+      </c>
+      <c r="I36" t="n">
         <v>11038</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>11778</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>12012</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>12256</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2094,42 +2202,45 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>31941</v>
+      </c>
+      <c r="C37" t="n">
         <v>33495</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>14381</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>13507</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>13049</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>12636</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>11520</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>11297</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11774</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>11365</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>10859</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>10782</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>10993</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>11127</v>
       </c>
     </row>
@@ -2140,42 +2251,45 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>345</v>
+      </c>
+      <c r="C38" t="n">
         <v>337</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>342</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>357</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>378</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>371</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>356</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>361</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>334</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>356</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>358</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>366</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>389</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>400</v>
       </c>
     </row>
@@ -2186,42 +2300,45 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>32286</v>
+      </c>
+      <c r="C39" t="n">
         <v>33832</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>14723</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>13864</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>13427</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>13007</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>11876</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>11658</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12108</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>11721</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>11217</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>11148</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11382</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>11527</v>
       </c>
     </row>
@@ -2235,39 +2352,42 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
         <v>612</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>571</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>444</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>557</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>633</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>472</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>723</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>646</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>542</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>579</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>385</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>334</v>
       </c>
     </row>
@@ -2281,39 +2401,42 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
         <v>242</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>200</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>148</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>209</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>201</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>179</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>289</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>278</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>259</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>422</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>357</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>212</v>
       </c>
     </row>
@@ -2327,39 +2450,42 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
         <v>1422</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>1385</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1354</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>1263</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>1241</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>1206</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>1133</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>1109</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1085</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>1042</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>1026</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>999</v>
       </c>
     </row>
@@ -2373,39 +2499,42 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
         <v>427</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>398</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>386</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>494</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>584</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>623</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>727</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>647</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>223</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>193</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>211</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>217</v>
       </c>
     </row>
@@ -2419,39 +2548,42 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
         <v>1412</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>1397</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>1381</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>1349</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>1331</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>1313</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>1278</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>1260</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1244</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>1219</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>1213</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>1210</v>
       </c>
     </row>
@@ -2474,30 +2606,33 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
         <v>35</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>25</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>38</v>
-      </c>
-      <c r="I45" t="n">
-        <v>43</v>
       </c>
       <c r="J45" t="n">
         <v>43</v>
       </c>
       <c r="K45" t="n">
+        <v>43</v>
+      </c>
+      <c r="L45" t="n">
         <v>45</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>23</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>34</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2520,30 +2655,33 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
         <v>867</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>877</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>888</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>610</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>638</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>645</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>636</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>682</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>722</v>
       </c>
     </row>
@@ -2575,21 +2713,24 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>1317</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>1260</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1558</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2597</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>2160</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>1847</v>
       </c>
     </row>
@@ -2600,42 +2741,45 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>31977</v>
+      </c>
+      <c r="C48" t="n">
         <v>33483</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>14350</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>13446</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>12956</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>12570</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>11425</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>11199</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>11666</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>11256</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>10728</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>10803</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>11000</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>11105</v>
       </c>
     </row>
@@ -2650,47 +2794,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -2701,42 +2848,45 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>7504</v>
+      </c>
+      <c r="C2" t="n">
         <v>11122</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>6570</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>6101</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>6788</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6550</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5475</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>6161</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>6111</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5446</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>7565</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>6051</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5465</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>5591</v>
       </c>
     </row>
@@ -2747,42 +2897,45 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4023</v>
+      </c>
+      <c r="C3" t="n">
         <v>6352</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>3567</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3132</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4384</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3119</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2292</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3417</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3367</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2887</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>5729</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>4695</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3508</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>3545</v>
       </c>
     </row>
@@ -2793,42 +2946,45 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2253</v>
+      </c>
+      <c r="C4" t="n">
         <v>1780</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1511</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1617</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1545</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1535</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1645</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1486</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1353</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1477</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1432</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>989</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1273</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1161</v>
       </c>
     </row>
@@ -2842,39 +2998,42 @@
         <v>443</v>
       </c>
       <c r="C5" t="n">
+        <v>443</v>
+      </c>
+      <c r="D5" t="n">
         <v>241</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>254</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>248</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>266</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>296</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>306</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>266</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>274</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>267</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>262</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>277</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>280</v>
       </c>
     </row>
@@ -2885,42 +3044,45 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>207</v>
+      </c>
+      <c r="C6" t="n">
         <v>229</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>165</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>147</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>160</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>165</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>142</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>139</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>148</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>139</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>132</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>145</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>133</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>137</v>
       </c>
     </row>
@@ -2931,42 +3093,45 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>6926</v>
+      </c>
+      <c r="C7" t="n">
         <v>8804</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5484</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>5150</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>6337</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>5085</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4375</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5348</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5134</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>4777</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>7560</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>6091</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5191</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>5172</v>
       </c>
     </row>
@@ -2977,11 +3142,11 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
@@ -2989,11 +3154,11 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -3004,15 +3169,18 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>26</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>-1</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>-2</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3023,42 +3191,45 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>580</v>
+      </c>
+      <c r="C9" t="n">
         <v>2332</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1086</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>951</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>451</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1467</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1100</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>813</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>977</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>669</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>31</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-41</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>272</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>435</v>
       </c>
     </row>
@@ -3069,42 +3240,45 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-283</v>
+      </c>
+      <c r="C10" t="n">
         <v>-253</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-134</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-118</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-146</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-147</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-142</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-127</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-82</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-103</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-107</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-75</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-56</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -3115,42 +3289,45 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>603</v>
+      </c>
+      <c r="C11" t="n">
         <v>46</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>443</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>440</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-154</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>325</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>6</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>362</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>605</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>314</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-196</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-654</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-318</v>
       </c>
     </row>
@@ -3161,42 +3338,45 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" t="n">
         <v>-207</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>309</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>322</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-300</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>178</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-136</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>235</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-82</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>502</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>207</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-271</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-710</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-374</v>
       </c>
     </row>
@@ -3207,42 +3387,45 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>900</v>
+      </c>
+      <c r="C13" t="n">
         <v>2125</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1395</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1273</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>151</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1645</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>964</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1048</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>895</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>1171</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>238</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-312</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-438</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>61</v>
       </c>
     </row>
@@ -3253,42 +3436,45 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>398</v>
+      </c>
+      <c r="C14" t="n">
         <v>530</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>466</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>440</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>22</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>449</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>154</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>165</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>205</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>342</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>131</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-123</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-328</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>-53</v>
       </c>
     </row>
@@ -3299,11 +3485,11 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
         <v>8</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
@@ -3314,29 +3500,32 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>-1</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>-5</v>
       </c>
       <c r="L15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M15" t="n">
         <v>-4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-3</v>
       </c>
       <c r="N15" t="n">
         <v>-3</v>
       </c>
+      <c r="O15" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3345,42 +3534,45 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>508</v>
+      </c>
+      <c r="C16" t="n">
         <v>1603</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>929</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>833</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>129</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>1196</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>809</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>883</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>690</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>824</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>102</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-193</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-113</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>111</v>
       </c>
     </row>
@@ -3391,42 +3583,45 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C17" t="n">
         <v>13</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-6</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>11</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-4</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-5</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>-41</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-9</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-5</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-2</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3437,42 +3632,45 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>513</v>
+      </c>
+      <c r="C18" t="n">
         <v>1590</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>930</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>839</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>118</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1200</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>814</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>883</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>731</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>833</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>96</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-188</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-111</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>106</v>
       </c>
     </row>
@@ -3483,19 +3681,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>-1</v>
       </c>
       <c r="D19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" t="n">
         <v>-2</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
@@ -3504,23 +3702,26 @@
         <v>-1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>-3</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>-1</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>-2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-1</v>
       </c>
       <c r="N19" t="n">
         <v>-1</v>
       </c>
+      <c r="O19" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3529,42 +3730,45 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>26</v>
+      </c>
+      <c r="C20" t="n">
         <v>28</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>18</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>17</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>15</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>21</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>18</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>6</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>28</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>27</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3575,42 +3779,45 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
         <v>-25</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>-34</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>-2</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-3</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>-53</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3621,26 +3828,26 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -3651,12 +3858,15 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>-1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3667,42 +3877,45 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C23" t="n">
         <v>-3</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-8</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>20</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>8</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>12</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-1</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-3</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>-6</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-2</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3713,42 +3926,45 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>12</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>37</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-7</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>27</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>19</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>11</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>3</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>8</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-48</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>23</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>24</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3759,42 +3975,45 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>535</v>
+      </c>
+      <c r="C25" t="n">
         <v>1603</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>941</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>870</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>122</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>1223</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>828</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>894</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>693</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>832</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>54</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-170</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-89</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>132</v>
       </c>
     </row>
@@ -3805,42 +4024,45 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>540</v>
+      </c>
+      <c r="C26" t="n">
         <v>1590</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>942</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>876</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>111</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>1227</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>833</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>894</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>734</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>841</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>48</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>-165</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-87</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>127</v>
       </c>
     </row>
@@ -3872,21 +4094,24 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>6111</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>5446</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>7565</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>6051</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>5465</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>5431</v>
       </c>
     </row>
@@ -3897,37 +4122,37 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>360</v>
+      </c>
+      <c r="C28" t="n">
         <v>354</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>313</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>314</v>
-      </c>
-      <c r="E28" t="n">
-        <v>313</v>
       </c>
       <c r="F28" t="n">
         <v>313</v>
       </c>
       <c r="G28" t="n">
+        <v>313</v>
+      </c>
+      <c r="H28" t="n">
         <v>315</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>317</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>322</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>324</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>328</v>
-      </c>
-      <c r="L28" t="n">
-        <v>327</v>
       </c>
       <c r="M28" t="n">
         <v>327</v>
@@ -3935,6 +4160,9 @@
       <c r="N28" t="n">
         <v>327</v>
       </c>
+      <c r="O28" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3943,13 +4171,13 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>360</v>
+      </c>
+      <c r="C29" t="n">
         <v>354</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>313</v>
-      </c>
-      <c r="D29" t="n">
-        <v>314</v>
       </c>
       <c r="E29" t="n">
         <v>314</v>
@@ -3958,19 +4186,19 @@
         <v>314</v>
       </c>
       <c r="G29" t="n">
+        <v>314</v>
+      </c>
+      <c r="H29" t="n">
         <v>316</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>318</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>323</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>325</v>
-      </c>
-      <c r="K29" t="n">
-        <v>328</v>
       </c>
       <c r="L29" t="n">
         <v>328</v>
@@ -3979,6 +4207,9 @@
         <v>328</v>
       </c>
       <c r="N29" t="n">
+        <v>328</v>
+      </c>
+      <c r="O29" t="n">
         <v>327</v>
       </c>
     </row>
@@ -4025,6 +4256,9 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4039,47 +4273,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
     </row>
@@ -4090,42 +4327,45 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2111</v>
+      </c>
+      <c r="C2" t="n">
         <v>1603</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1891</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>962</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>129</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>2888</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1692</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>883</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1616</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>926</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>102</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>-195</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>-2</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>111</v>
       </c>
     </row>
@@ -4136,42 +4376,45 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>2368</v>
+      </c>
+      <c r="C3" t="n">
         <v>1202</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1945</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1300</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>640</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2049</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1388</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>694</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1840</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1219</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>605</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1810</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1207</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>602</v>
       </c>
     </row>
@@ -4182,42 +4425,45 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>740</v>
+      </c>
+      <c r="C4" t="n">
         <v>440</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>248</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-98</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>358</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>191</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>9</v>
-      </c>
-      <c r="I4" t="n">
-        <v>189</v>
       </c>
       <c r="J4" t="n">
         <v>189</v>
       </c>
       <c r="K4" t="n">
+        <v>189</v>
+      </c>
+      <c r="L4" t="n">
         <v>-33</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>-915</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>-707</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>-307</v>
       </c>
     </row>
@@ -4228,42 +4474,45 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-589</v>
+      </c>
+      <c r="C5" t="n">
         <v>-1040</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>328</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>188</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>356</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-1161</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-776</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-186</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>146</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>281</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>273</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>544</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>31</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>75</v>
       </c>
     </row>
@@ -4274,42 +4523,45 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-419</v>
+      </c>
+      <c r="C6" t="n">
         <v>-17</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-588</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-336</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-44</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-475</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-197</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-192</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-154</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-270</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-187</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1032</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>800</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>271</v>
       </c>
     </row>
@@ -4320,42 +4572,45 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" t="n">
         <v>27</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>256</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>275</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>268</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>115</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>11</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-47</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>-490</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-414</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>27</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>25</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4366,42 +4621,45 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-240</v>
+      </c>
+      <c r="C8" t="n">
         <v>-199</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>-74</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-21</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>47</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-161</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-65</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>-41</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>147</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>103</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>-54</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>304</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>459</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>256</v>
       </c>
     </row>
@@ -4412,42 +4670,45 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>307</v>
+      </c>
+      <c r="C9" t="n">
         <v>323</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-184</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>208</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-15</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1083</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>771</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>464</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>942</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>1298</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>513</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-150</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>60</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-78</v>
       </c>
     </row>
@@ -4458,42 +4719,45 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-63</v>
+      </c>
+      <c r="C10" t="n">
         <v>106</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-62</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>17</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>98</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>31</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>58</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>114</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>90</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>124</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>168</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-166</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-88</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>82</v>
       </c>
     </row>
@@ -4504,42 +4768,45 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-1277</v>
+      </c>
+      <c r="C11" t="n">
         <v>-1377</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-25</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-229</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-290</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-38</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-207</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-382</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-1526</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>-1725</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-1516</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>789</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>385</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -4550,42 +4817,45 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-52</v>
+      </c>
+      <c r="C12" t="n">
         <v>-15</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>49</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>18</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>26</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>159</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>129</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>74</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-36</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-48</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-23</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-163</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-167</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-31</v>
       </c>
     </row>
@@ -4596,42 +4866,45 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-357</v>
+      </c>
+      <c r="C13" t="n">
         <v>249</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-192</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-242</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-486</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>1495</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>868</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>297</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-222</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-474</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-261</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>766</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1123</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1169</v>
       </c>
     </row>
@@ -4642,42 +4915,45 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
         <v>103</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>423</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>209</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>120</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>154</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-86</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>159</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>277</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>160</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>163</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>364</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>289</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>254</v>
       </c>
     </row>
@@ -4688,42 +4964,45 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-200</v>
+      </c>
+      <c r="C15" t="n">
         <v>-191</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-193</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-181</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-174</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-178</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-188</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-177</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-46</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-18</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-10</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>-229</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-213</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-204</v>
       </c>
     </row>
@@ -4734,42 +5013,45 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-813</v>
+      </c>
+      <c r="C16" t="n">
         <v>-789</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>-390</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>-598</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-470</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-7767</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-4925</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>-2392</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-4892</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-2451</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-761</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-3756</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-1946</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-909</v>
       </c>
     </row>
@@ -4780,42 +5062,45 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>1553</v>
+      </c>
+      <c r="C17" t="n">
         <v>425</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>3432</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1584</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>107</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-1448</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-1336</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-723</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-2119</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-1126</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-934</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>69</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1263</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>1351</v>
       </c>
     </row>
@@ -4826,42 +5111,45 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-2521</v>
+      </c>
+      <c r="C18" t="n">
         <v>-1275</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-1963</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-1573</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-806</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-1836</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-1284</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-738</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-1735</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-1336</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-660</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-1090</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-800</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-410</v>
       </c>
     </row>
@@ -4872,42 +5160,45 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>4737</v>
+      </c>
+      <c r="C19" t="n">
         <v>2504</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>5525</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>3830</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>2084</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>4934</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>2890</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1779</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>4221</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>3116</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1977</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>3034</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>2188</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>1130</v>
       </c>
     </row>
@@ -4918,42 +5209,45 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>-4911</v>
+      </c>
+      <c r="C20" t="n">
         <v>-2572</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>-5773</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>-3999</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-2152</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>-5140</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>-3043</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>-1847</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>-4374</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>-3203</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>-2030</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>-3212</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>-2323</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>-1193</v>
       </c>
     </row>
@@ -4967,26 +5261,26 @@
         <v>-2537</v>
       </c>
       <c r="C21" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="D21" t="n">
         <v>-13</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>-10</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-5</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-22</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-15</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-14</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -5000,6 +5294,9 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5010,42 +5307,45 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>131</v>
+      </c>
+      <c r="C22" t="n">
         <v>148</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>-6</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>-7</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>16</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>6</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>-1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-15</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-12</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-18</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -5056,42 +5356,45 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>-5101</v>
+      </c>
+      <c r="C23" t="n">
         <v>-3732</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-2221</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>-1758</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-886</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>5056</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>2650</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>830</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>2179</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>171</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>219</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1871</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>701</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>404</v>
       </c>
     </row>
@@ -5102,11 +5405,11 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2586</v>
+      </c>
+      <c r="C24" t="n">
         <v>1957</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
@@ -5114,32 +5417,35 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>-1105</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-625</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>165</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-959</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-524</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-754</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-209</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-702</v>
       </c>
       <c r="N24" t="n">
         <v>-702</v>
       </c>
+      <c r="O24" t="n">
+        <v>-702</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5148,19 +5454,19 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C25" t="n">
         <v>3000</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>1650</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>900</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>200</v>
@@ -5169,21 +5475,24 @@
         <v>200</v>
       </c>
       <c r="I25" t="n">
+        <v>200</v>
+      </c>
+      <c r="J25" t="n">
         <v>527</v>
-      </c>
-      <c r="J25" t="n">
-        <v>500</v>
       </c>
       <c r="K25" t="n">
         <v>500</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5194,11 +5503,11 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-3500</v>
+      </c>
+      <c r="C26" t="n">
         <v>-1500</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
@@ -5206,16 +5515,16 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>-739</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-539</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-500</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-200</v>
       </c>
       <c r="J26" t="n">
         <v>-200</v>
@@ -5224,12 +5533,15 @@
         <v>-200</v>
       </c>
       <c r="L26" t="n">
-        <v>-1180</v>
+        <v>-200</v>
       </c>
       <c r="M26" t="n">
         <v>-1180</v>
       </c>
       <c r="N26" t="n">
+        <v>-1180</v>
+      </c>
+      <c r="O26" t="n">
         <v>-300</v>
       </c>
     </row>
@@ -5240,11 +5552,11 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>5001</v>
+      </c>
+      <c r="C27" t="n">
         <v>2770</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
@@ -5252,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>900</v>
@@ -5261,21 +5573,24 @@
         <v>900</v>
       </c>
       <c r="I27" t="n">
+        <v>900</v>
+      </c>
+      <c r="J27" t="n">
         <v>3192</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>1791</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>1353</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>9</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>6</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5286,42 +5601,45 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>-5352</v>
+      </c>
+      <c r="C28" t="n">
         <v>-5254</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>-1036</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>-1008</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>-57</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>-99</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>-65</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>-32</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>-150</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>-121</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>-30</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>-1143</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>-1109</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>-1058</v>
       </c>
     </row>
@@ -5332,42 +5650,45 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>-78</v>
+      </c>
+      <c r="C29" t="n">
         <v>-88</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>-98</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>-141</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>-229</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>-5</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>-35</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>-38</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>6</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>-10</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>-22</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>-43</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>-28</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>-23</v>
       </c>
     </row>
@@ -5378,42 +5699,45 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>877</v>
+      </c>
+      <c r="C30" t="n">
         <v>730</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>-249</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>-893</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>-408</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>-2180</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>-1385</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>84</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1389</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>752</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>523</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>-1213</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>-1614</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-635</v>
       </c>
     </row>
@@ -5424,42 +5748,45 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>-2671</v>
+      </c>
+      <c r="C31" t="n">
         <v>-2577</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>962</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>-1067</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>-1187</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>1428</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>-71</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>191</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1449</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>-203</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>-192</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>727</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>350</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>1120</v>
       </c>
     </row>
@@ -5473,7 +5800,7 @@
         <v>3748</v>
       </c>
       <c r="C32" t="n">
-        <v>3129</v>
+        <v>3748</v>
       </c>
       <c r="D32" t="n">
         <v>3129</v>
@@ -5482,7 +5809,7 @@
         <v>3129</v>
       </c>
       <c r="F32" t="n">
-        <v>454</v>
+        <v>3129</v>
       </c>
       <c r="G32" t="n">
         <v>454</v>
@@ -5491,7 +5818,7 @@
         <v>454</v>
       </c>
       <c r="I32" t="n">
-        <v>528</v>
+        <v>454</v>
       </c>
       <c r="J32" t="n">
         <v>528</v>
@@ -5500,7 +5827,7 @@
         <v>528</v>
       </c>
       <c r="L32" t="n">
-        <v>576</v>
+        <v>528</v>
       </c>
       <c r="M32" t="n">
         <v>576</v>
@@ -5508,6 +5835,9 @@
       <c r="N32" t="n">
         <v>576</v>
       </c>
+      <c r="O32" t="n">
+        <v>576</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5519,7 +5849,7 @@
         <v>17507</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>17507</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -5552,6 +5882,9 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5565,7 +5898,7 @@
         <v>2290</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2290</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -5598,6 +5931,9 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5608,26 +5944,26 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>-868</v>
+      </c>
+      <c r="C35" t="n">
         <v>-889</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>188</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>-6</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
         <v>-1475</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>-389</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -5644,6 +5980,9 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5654,29 +5993,29 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>-240</v>
+      </c>
+      <c r="C36" t="n">
         <v>-272</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>-51</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>-118</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>-259</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>238</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>97</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>-32</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
@@ -5684,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>20</v>
@@ -5692,6 +6031,9 @@
       <c r="N36" t="n">
         <v>20</v>
       </c>
+      <c r="O36" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5700,49 +6042,52 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>-2280</v>
+      </c>
+      <c r="C37" t="n">
         <v>-155</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>-914</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>-793</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>-272</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>-1331</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>-1220</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>-610</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>-909</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>-584</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>-249</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Collection of Retained Interest in Securitized Receivables</t>
+          <t>Proceeds from Contributions from Affiliates</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -5752,43 +6097,46 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F38" t="n">
-        <v>7104</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1644</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4058</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1582</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>926</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>3095</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1595</v>
+        <v>1750</v>
       </c>
       <c r="N38" t="n">
-        <v>853</v>
+        <v>1750</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1750</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Supplemental Deferred Purchase Price</t>
+          <t>Proceeds from Collection of Retained Interest in Securitized Receivables</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -5804,47 +6152,50 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>7682</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>4455</v>
+        <v>7104</v>
       </c>
       <c r="H39" t="n">
-        <v>1812</v>
+        <v>4096</v>
       </c>
       <c r="I39" t="n">
-        <v>5288</v>
+        <v>1644</v>
       </c>
       <c r="J39" t="n">
-        <v>2335</v>
+        <v>4058</v>
       </c>
       <c r="K39" t="n">
-        <v>794</v>
+        <v>1582</v>
       </c>
       <c r="L39" t="n">
-        <v>3733</v>
+        <v>926</v>
       </c>
       <c r="M39" t="n">
-        <v>1860</v>
+        <v>3095</v>
       </c>
       <c r="N39" t="n">
-        <v>918</v>
+        <v>1595</v>
+      </c>
+      <c r="O39" t="n">
+        <v>853</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Contributions from Affiliates</t>
+          <t>Supplemental Deferred Purchase Price</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -5853,28 +6204,31 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>7682</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>4455</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1812</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>5288</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2335</v>
       </c>
       <c r="L40" t="n">
-        <v>1750</v>
+        <v>794</v>
       </c>
       <c r="M40" t="n">
-        <v>1750</v>
+        <v>3733</v>
       </c>
       <c r="N40" t="n">
-        <v>1750</v>
+        <v>1860</v>
+      </c>
+      <c r="O40" t="n">
+        <v>918</v>
       </c>
     </row>
     <row r="41">
@@ -5893,33 +6247,36 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>10</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>20</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>54</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>110</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>-63</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>-44</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>11</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>-17</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>-141</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>-119</v>
       </c>
     </row>
@@ -5948,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>7</v>
-      </c>
-      <c r="I42" t="n">
-        <v>24</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
@@ -5960,12 +6317,15 @@
         <v>24</v>
       </c>
       <c r="L42" t="n">
+        <v>24</v>
+      </c>
+      <c r="M42" t="n">
         <v>41</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>39</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>28</v>
       </c>
     </row>
@@ -6006,7 +6366,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>-258</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>-258</v>
@@ -6014,6 +6374,9 @@
       <c r="N43" t="n">
         <v>-258</v>
       </c>
+      <c r="O43" t="n">
+        <v>-258</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6043,21 +6406,24 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>762</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>342</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>333</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>335</v>
       </c>
     </row>
@@ -6092,18 +6458,21 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>-26</v>
       </c>
       <c r="L45" t="n">
-        <v>-13</v>
+        <v>-26</v>
       </c>
       <c r="M45" t="n">
         <v>-13</v>
       </c>
       <c r="N45" t="n">
+        <v>-13</v>
+      </c>
+      <c r="O45" t="n">
         <v>-16</v>
       </c>
     </row>
@@ -6114,42 +6483,45 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>309</v>
+      </c>
+      <c r="C46" t="n">
         <v>155</v>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>366</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>244</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>122</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>333</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>222</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>112</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>277</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>185</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>93</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>139</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>93</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>46</v>
       </c>
     </row>
@@ -6160,42 +6532,45 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1971</v>
       </c>
       <c r="C47" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>400</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F47" t="n">
-        <v>999000</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>999000</v>
       </c>
       <c r="H47" t="n">
+        <v>999000</v>
+      </c>
+      <c r="I47" t="n">
         <v>499000</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>750000</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>499000</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>231000</v>
       </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
         <v>0</v>
       </c>
     </row>
